--- a/web-console-ui-translations/dist/translations.xlsx
+++ b/web-console-ui-translations/dist/translations.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>ospite</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Arbeitsbereich Dateien</t>
+          <t>Arbeitsbereich-Dateien</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Apprezziamo il fatto che abbia dedicato del tempo a darci un feedback e lavoreremo per
+          <t>Apprezziamo il fatto che abbia dedicato del tempo a fornirci un feedback e lavoreremo per
           risolvere i problemi che ha elencato.</t>
         </is>
       </c>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Presente</t>
+          <t>Invia</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Consenti l'accesso degli ospiti allo spazio di lavoro $t(assets)</t>
+          <t>Consenti l'accesso ospite allo spazio di lavoro $t(assets)</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>No $t(assets) $t(selected)@</t>
+          <t>No $t(assets) $t(selected)</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>In attesa della guida...</t>
+          <t>In attesa dell'host...</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Desidera mantenere la SuperFreeze come risorsa?</t>
+          <t>Vuole mantenere il SuperFreeze come asset?</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Funktion aktiviert ist, können Gäste an der Besprechung teilnehmen, ohne dass ein Host anwesend ist.</t>
+          <t>Wenn diese Funktion aktiviert ist, können Gäste an einem Meeting teilnehmen, ohne dass ein Host anwesend ist.</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Quando è abilitato, gli Host e gli Ospiti possono utilizzare le funzioni relative allo storage, compresa la Libreria delle risorse.</t>
+          <t>Quando è abilitato, gli Host e gli Ospiti possono utilizzare le funzioni relative all'archiviazione, compresa la Libreria di risorse.</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Funktion aktiviert ist, können Hosts und Gäste speicherbezogene Funktionen, einschließlich der Asset-Bibliothek, nutzen.</t>
+          <t>Wenn diese Option aktiviert ist, können Hosts und Gäste speicherbezogene Funktionen, einschließlich der Asset-Bibliothek, nutzen.</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Tutti gli ospiti</t>
+          <t>Tutti gli host</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>Inserisca l'indirizzo e-mail associato al suo conto$t(avatour)@ e la password temporanea ricevuta
+          <t>Inserisca l'indirizzo e-mail associato al suo conto$t(avatour) e la password temporanea ricevuta
  e la password temporanea che ha ricevuto, quindi
  scegliere e confermare una nuova password. La sua password deve
  essere di 8 caratteri e contenere lettere maiuscole e minuscole e numeri.</t>
@@ -8181,7 +8181,7 @@
       <c r="C351" s="4" t="inlineStr">
         <is>
           <t>&lt;1&gt;Are you sure you want to reset the password for {{email}}?&lt;/1&gt; &lt;1&gt;This will disable their current password and send them an email
-with instructions for setting a new password.&lt;/1&gt;@
+with instructions for setting a new password.&lt;/1&gt;
  &lt;1&gt;Note: Password reset email links expire after 24 hours.&lt;/1&gt;</t>
         </is>
       </c>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Inserisca l'indirizzo e-mail associato al suo$t(avatour)@ account e riceverà un link per reimpostare la password
+          <t>Inserisca l'indirizzo e-mail associato al suo$t(avatour) account e riceverà un link per reimpostare la password
  e riceverà un link per reimpostare la password.</t>
         </is>
       </c>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o si rivolga a &lt;0&gt;support@avatour.live&lt;/0&gt; per ricevere assistenza.</t>
+          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o si rivolga a &lt;0&gt;supportavatour.live&lt;/0&gt; per ricevere assistenza.</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Per cambiare il suo dominio, contatti &lt;0&gt;support@avatour.live&lt;/0&gt;@</t>
+          <t>Per cambiare il suo dominio, contatti &lt;0&gt;supportavatour.live&lt;/0&gt;</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>Non ha domini personalizzati. Contatti &lt;0&gt;support@avatour.live&lt;/0&gt; per richiedere un nuovo dominio personalizzato.</t>
+          <t>Non ha domini personalizzati. Contatti &lt;0&gt;supportavatour.live&lt;/0&gt; per richiedere un nuovo dominio personalizzato.</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>In attesa che l'host inizi la riunione...</t>
+          <t>In attesa che Host inizi la riunione...</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Sulla base dei &lt;1&gt;{{participantsUsed}}&lt;/1&gt; partecipanti con ubicazione nota, tutte le riunioni combinate hanno evitato un totale di &lt;3&gt;{{miles}} miles&lt;/3&gt;@ di viaggi aerei.</t>
+          <t>Sulla base dei &lt;1&gt;{{participantsUsed}}&lt;/1&gt; partecipanti con ubicazione nota, tutte le riunioni combinate hanno evitato un totale di &lt;3&gt;{{miles}} miles&lt;/3&gt; di viaggi aerei.</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">

--- a/web-console-ui-translations/dist/translations.xlsx
+++ b/web-console-ui-translations/dist/translations.xlsx
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Niemand hat sich dem Meeting angeschlossen</t>
+          <t>Niemand hat an dem Meeting teilgenommen</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Verbindung zur$t(avatour) Cloud...</t>
+          <t>Verbinden mit$t(avatour) Cloud...</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Das Raumlimit wurde erreicht. Sie müssen warten, bis einige Teilnehmer das Meeting verlassen</t>
+          <t>Das Raumlimit wurde erreicht, Sie müssen warten, bis einige Teilnehmer das Meeting verlassen</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Verbindung zur$t(avatour) Cloud...</t>
+          <t>Verbinden mit$t(avatour) Cloud...</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Video war verzögert</t>
+          <t>Video wurde verzögert</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Sie können Ihre Kamera und Ihr Mikrofon während des Meetings nach Bedarf deaktivieren/aktivieren</t>
+          <t>Sie können Ihre Kamera und Ihr Mikrofon während des Meetings bei Bedarf weiterhin deaktivieren/aktivieren</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Funktion aktiviert ist, müssen sich Gäste anmelden, um an der Besprechung teilzunehmen.</t>
+          <t>Wenn diese Funktion aktiviert ist, müssen sich Gäste anmelden, um am Meeting teilzunehmen.</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Option aktiviert ist, beginnt die Aufnahme von Meetings automatisch beim Start. Lassen Sie die Option deaktiviert, um als Host die Aufzeichnung manuell zu starten und zu beenden.</t>
+          <t>Wenn diese Option aktiviert ist, beginnt die Aufzeichnung von Meetings automatisch mit dem Start. Lassen Sie die Option deaktiviert, um als Host die Aufzeichnung manuell zu starten und zu beenden.</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Zustimmung für aufgezeichnete Meetingen verlangen</t>
+          <t>Zustimmung für aufgezeichnete Meetings verlangen</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Gäste werden gebeten, den Bedingungen für die Aufzeichnung zuzustimmen, bevor sie an einer Meeting mit aktivierter Aufzeichnung teilnehmen.</t>
+          <t>Gäste werden gebeten, den Bedingungen für die Aufzeichnung zuzustimmen, bevor sie an einem Meeting mit aktivierter Aufzeichnung teilnehmen.</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Option deaktiviert ist, können Gäste auch ohne Host teilnehmen. Wenn diese Option aktiviert ist, muss der Host Gäste zulassen und das Meeting endet, wenn der Host geht.</t>
+          <t>Wenn diese Option deaktiviert ist, können Gäste auch ohne Host teilnehmen. Wenn diese Option aktiviert ist, muss der Host Gäste zulassen, und das Meeting endet, wenn der Host geht.</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Passwort wurde geändert</t>
+          <t>Das Passwort wurde geändert</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Besprechungscode ist ungültig</t>
+          <t>Meeting Code ist ungültig</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>SuperFreeze ha richiesto</t>
+          <t>SuperFreeze richiesto</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>La batteria del dispositivo di cattura è scarica</t>
+          <t>La batteria del dispositivo di acquisizione è scarica</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Erlauben Sie Meetings ohne Host</t>
+          <t>Meetings ohne Host zulassen</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Option aktiviert ist, können Hosts und Gäste speicherbezogene Funktionen, einschließlich der Asset-Bibliothek, nutzen.</t>
+          <t>Wenn diese Funktion aktiviert ist, können Hosts und Gäste speicherbezogene Funktionen, einschließlich der Asset-Bibliothek, nutzen.</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Wenn diese Funktion aktiviert ist, hat jeder, der den Arbeitsbereich verlinkt hat, Viewer-Zugriff auf den Arbeitsbereich und seine Assets. (Hinweis: Nicht-Kollaborateure sehen keine Besprechungsinformationen / Schaltfläche Beitreten)</t>
+          <t>Wenn diese Funktion aktiviert ist, hat jeder, der den Arbeitsbereich verlinkt hat, Viewer-Zugriff auf den Arbeitsbereich und seine Assets. (Hinweis: Nicht-Kollaborateure sehen keine Meeting-Infos / Beitrittsschaltfläche)</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Una volta che la licenza di un host è stata disattivata, l'host non avrà più
+          <t>Una volta che la licenza di un host viene disattivata, l'host non avrà più
  l'accesso ai suoi spazi di lavoro o alla libreria di risorse</t>
         </is>
       </c>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>gesamtzahl der Meetingen</t>
+          <t>gesamtzahl der Meetings</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Meetings ansehen</t>
+          <t>Meetings anzeigen</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>Keine Meeting gefunden</t>
+          <t>Keine Meetings gefunden</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>nahm an dem Meeting teil</t>
+          <t>an dem Meeting teilgenommen</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>Inserisca l'indirizzo e-mail associato al suo conto$t(avatour) e la password temporanea ricevuta
+          <t>Inserisca l'indirizzo e-mail associato al suo conto$t(avatour)@ e la password temporanea ricevuta
  e la password temporanea che ha ricevuto, quindi
  scegliere e confermare una nuova password. La sua password deve
  essere di 8 caratteri e contenere lettere maiuscole e minuscole e numeri.</t>
@@ -8181,7 +8181,7 @@
       <c r="C351" s="4" t="inlineStr">
         <is>
           <t>&lt;1&gt;Are you sure you want to reset the password for {{email}}?&lt;/1&gt; &lt;1&gt;This will disable their current password and send them an email
-with instructions for setting a new password.&lt;/1&gt;
+with instructions for setting a new password.&lt;/1&gt;@
  &lt;1&gt;Note: Password reset email links expire after 24 hours.&lt;/1&gt;</t>
         </is>
       </c>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>Wenn ein Konto mit dieser E-Mail-Adresse existiert, wurde ein Link zum Zurücksetzen des Passworts gesendet. Bitte &lt;1&gt; check
+          <t>Wenn ein Konto mit dieser E-Mail existiert, wurde ein Link zum Zurücksetzen des Passworts gesendet. Bitte &lt;1&gt; check
  your spam folder &lt;/1&gt;, wenn Sie ihn nicht in Ihrem Posteingang erhalten.</t>
         </is>
       </c>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Inserisca l'indirizzo e-mail associato al suo$t(avatour) account e riceverà un link per reimpostare la password
+          <t>Inserisca l'indirizzo e-mail associato al suo$t(avatour)@ account e riceverà un link per reimpostare la password
  e riceverà un link per reimpostare la password.</t>
         </is>
       </c>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o si rivolga a &lt;0&gt;supportavatour.live&lt;/0&gt; per ricevere assistenza.</t>
+          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o si rivolga a &lt;0&gt;support@avatour.live&lt;/0&gt; per ricevere assistenza.</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Option aktiviert ist, müssen die Teilnehmer ein Kennwort eingeben, um der Besprechung beizutreten.</t>
+          <t>Wenn diese Option aktiviert ist, müssen die Teilnehmer ein Passwort eingeben, um dem Meeting beizutreten.</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Per cambiare il suo dominio, contatti &lt;0&gt;supportavatour.live&lt;/0&gt;</t>
+          <t>Per cambiare il suo dominio, contatti &lt;0&gt;support@avatour.live&lt;/0&gt;</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>Non ha domini personalizzati. Contatti &lt;0&gt;supportavatour.live&lt;/0&gt; per richiedere un nuovo dominio personalizzato.</t>
+          <t>Non ha domini personalizzati. Contatti &lt;0&gt;support@avatour.live&lt;/0&gt; per richiedere un nuovo dominio personalizzato.</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>meeting-Infos</t>
+          <t>meeting-Informationen</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Sie können die Igluprojektion während der Besprechung einschalten, indem Sie auf 'Mehr' -&gt; 'Igluprojektion' zugreifen</t>
+          <t>Sie können die Igloo-Projektion während eines Meetings umschalten, indem Sie auf 'Mehr' -&gt; 'Igloo-Projektion' zugreifen</t>
         </is>
       </c>
     </row>
@@ -9312,12 +9312,12 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>In attesa che Host inizi la riunione...</t>
+          <t>In attesa che l'host inizi la riunione...</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>Ich warte darauf, dass der Host das Meeting beginnt...</t>
+          <t>Warten auf den Host, um das Meeting zu beginnen...</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Jüngste Meeting</t>
+          <t>Letzte Meetings</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>Kommende Meeting</t>
+          <t>Anstehende Meetings</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>Meetingscode</t>
+          <t>Meeting Code</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>Weitere vergangene Meeting anzeigen</t>
+          <t>Weitere vergangene Meetings anzeigen</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>meetingraum betreten</t>
+          <t>meeting-Raum beitreten</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>Keine Meeting im Gange</t>
+          <t>Kein Meeting im Gange</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>Ausgehend von den &lt;1&gt;{{participantsUsed}}&lt;/1&gt; Teilnehmern mit bekanntem Aufenthaltsort, wurden bei diesem Meeting insgesamt &lt;3&gt;{{miles}} miles&lt;/3&gt; Flugreisen vermieden.</t>
+          <t>Ausgehend von den &lt;1&gt;{{participantsUsed}}&lt;/1&gt; Teilnehmern mit bekannten Standorten wurden bei diesem Meeting insgesamt &lt;3&gt;{{miles}} miles&lt;/3&gt; Flugreisen vermieden.</t>
         </is>
       </c>
     </row>
@@ -10701,12 +10701,12 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Sulla base dei &lt;1&gt;{{participantsUsed}}&lt;/1&gt; partecipanti con ubicazione nota, tutte le riunioni combinate hanno evitato un totale di &lt;3&gt;{{miles}} miles&lt;/3&gt; di viaggi aerei.</t>
+          <t>Sulla base dei &lt;1&gt;{{participantsUsed}}&lt;/1&gt; partecipanti con ubicazione nota, tutte le riunioni combinate hanno evitato un totale di &lt;3&gt;{{miles}} miles&lt;/3&gt;@ di viaggi aerei.</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>Basierend auf den &lt;1&gt;{{participantsUsed}}&lt;/1&gt; Teilnehmern mit bekanntem Aufenthaltsort, wurden bei allen Meeting zusammen insgesamt &lt;3&gt;{{miles}} miles&lt;/3&gt; Flugreisen vermieden.</t>
+          <t>Ausgehend von den &lt;1&gt;{{participantsUsed}}&lt;/1&gt; Teilnehmern mit bekanntem Aufenthaltsort, wurden bei allen Meetings zusammen insgesamt &lt;3&gt;{{miles}} miles&lt;/3&gt; Flugreisen vermieden.</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>Sie sind bereits auf einem anderen Gerät oder in einem anderen Browser-Tab eingeloggt. Schließen Sie die andere Meeting, oder nehmen Sie hier als Gast mit dem Meeting-Code teil.</t>
+          <t>Sie sind bereits auf einem anderen Gerät oder in einem anderen Browser-Tab eingeloggt. Schließen Sie die andere Meeting, oder treten Sie hier als Gast mit dem Meeting-Code ein.</t>
         </is>
       </c>
     </row>

--- a/web-console-ui-translations/dist/translations.xlsx
+++ b/web-console-ui-translations/dist/translations.xlsx
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Verbinden mit$t(avatour) Cloud...</t>
+          <t>Verbindung zur$t(avatour) Cloud...</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Verbinden mit$t(avatour) Cloud...</t>
+          <t>Verbindung zur$t(avatour) Cloud...</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Video wurde verzögert</t>
+          <t>Video war verzögert</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Apprezziamo il fatto che abbia dedicato del tempo a fornirci un feedback e lavoreremo per
+          <t>Apprezziamo il fatto che abbia dedicato del tempo a darci un feedback e lavoreremo per
           risolvere i problemi che ha elencato.</t>
         </is>
       </c>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Das Passwort wurde geändert</t>
+          <t>Passwort wurde geändert</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>La batteria del dispositivo di acquisizione è scarica</t>
+          <t>La batteria del dispositivo di cattura è scarica</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Quando è abilitato, gli Host e gli Ospiti possono utilizzare le funzioni relative all'archiviazione, compresa la Libreria di risorse.</t>
+          <t>Quando è abilitato, gli Host e gli Ospiti possono utilizzare le funzioni relative allo storage, compresa la Libreria delle risorse.</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Funktion aktiviert ist, können Hosts und Gäste speicherbezogene Funktionen, einschließlich der Asset-Bibliothek, nutzen.</t>
+          <t>Wenn diese Option aktiviert ist, können Hosts und Gäste speicherbezogene Funktionen, einschließlich der Asset-Bibliothek, nutzen.</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Una volta che la licenza di un host viene disattivata, l'host non avrà più
+          <t>Una volta che la licenza di un host è stata disattivata, l'host non avrà più
  l'accesso ai suoi spazi di lavoro o alla libreria di risorse</t>
         </is>
       </c>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>Inserisca l'indirizzo e-mail associato al suo conto$t(avatour)@ e la password temporanea ricevuta
+          <t>Inserisca l'indirizzo e-mail associato al suo conto$t(avatour) e la password temporanea ricevuta
  e la password temporanea che ha ricevuto, quindi
  scegliere e confermare una nuova password. La sua password deve
  essere di 8 caratteri e contenere lettere maiuscole e minuscole e numeri.</t>
@@ -8181,7 +8181,7 @@
       <c r="C351" s="4" t="inlineStr">
         <is>
           <t>&lt;1&gt;Are you sure you want to reset the password for {{email}}?&lt;/1&gt; &lt;1&gt;This will disable their current password and send them an email
-with instructions for setting a new password.&lt;/1&gt;@
+with instructions for setting a new password.&lt;/1&gt;
  &lt;1&gt;Note: Password reset email links expire after 24 hours.&lt;/1&gt;</t>
         </is>
       </c>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>Wenn ein Konto mit dieser E-Mail existiert, wurde ein Link zum Zurücksetzen des Passworts gesendet. Bitte &lt;1&gt; check
+          <t>Wenn ein Konto mit dieser E-Mail-Adresse existiert, wurde ein Link zum Zurücksetzen des Passworts gesendet. Bitte &lt;1&gt; check
  your spam folder &lt;/1&gt;, wenn Sie ihn nicht in Ihrem Posteingang erhalten.</t>
         </is>
       </c>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Inserisca l'indirizzo e-mail associato al suo$t(avatour)@ account e riceverà un link per reimpostare la password
+          <t>Inserisca l'indirizzo e-mail associato al suo$t(avatour) account e riceverà un link per reimpostare la password
  e riceverà un link per reimpostare la password.</t>
         </is>
       </c>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o si rivolga a &lt;0&gt;support@avatour.live&lt;/0&gt; per ricevere assistenza.</t>
+          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o contatti &lt;0&gt;support@avatour.live&lt;/0&gt; per ricevere assistenza.</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Aktivieren Sie Benachrichtigungen</t>
+          <t>Benachrichtigungen einschalten</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Abilita l'Igloo</t>
+          <t>Abilita Igloo</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Sulla base dei &lt;1&gt;{{participantsUsed}}&lt;/1&gt; partecipanti con ubicazione nota, tutte le riunioni combinate hanno evitato un totale di &lt;3&gt;{{miles}} miles&lt;/3&gt;@ di viaggi aerei.</t>
+          <t>Sulla base dei &lt;1&gt;{{participantsUsed}}&lt;/1&gt; partecipanti con ubicazione nota, tutte le riunioni combinate hanno evitato un totale di &lt;3&gt;{{miles}} miles&lt;/3&gt; di viaggi aerei.</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">

--- a/web-console-ui-translations/dist/translations.xlsx
+++ b/web-console-ui-translations/dist/translations.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>immagine</t>
+          <t>Immagine</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>bild</t>
+          <t>Bild</t>
         </is>
       </c>
     </row>
@@ -548,12 +548,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>immagine 360</t>
+          <t>Immagine 360</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>bild 360</t>
+          <t>Bild 360</t>
         </is>
       </c>
     </row>
@@ -570,12 +570,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>video 360</t>
+          <t>Video 360</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>video 360</t>
+          <t>Video 360</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>riunione</t>
+          <t>Riunione</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>riunione</t>
+          <t>Riunione</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>presente</t>
+          <t>Presente</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>präsentieren</t>
+          <t>Präsentieren</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>lingua</t>
+          <t>Lingua</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>sprache</t>
+          <t>Sprache</t>
         </is>
       </c>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>buono</t>
+          <t>Buono</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>Gut</t>
         </is>
       </c>
     </row>
@@ -724,12 +724,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>cattivo</t>
+          <t>Cattivo</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>schlecht</t>
+          <t>Schlecht</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>keine</t>
+          <t>Keine</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>sì</t>
+          <t>Sì</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>confermare</t>
+          <t>Confermare</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>bestätigen</t>
+          <t>Bestätigen</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>scartare</t>
+          <t>Scartare</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>verwerfen</t>
+          <t>Verwerfen</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>ospite</t>
+          <t>Ospite</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>gast</t>
+          <t>Gast</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>ospiti</t>
+          <t>Ospiti</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>gäste</t>
+          <t>Gäste</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>Host</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>Host</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>microfono</t>
+          <t>Microfono</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>mikrofon</t>
+          <t>Mikrofon</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>audio</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>audio</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>altoparlanti</t>
+          <t>Altoparlanti</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>lautsprecher</t>
+          <t>Lautsprecher</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>codice</t>
+          <t>Codice</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>Code</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>passwort</t>
+          <t>Passwort</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>e-mail</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>e-Mail</t>
+          <t>E-Mail</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>cambiare la password</t>
+          <t>Cambiare la password</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>passwort ändern</t>
+          <t>Passwort ändern</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>salvare la password</t>
+          <t>Salvare la password</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>passwort speichern</t>
+          <t>Passwort speichern</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>salvare</t>
+          <t>Salvare</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>speichern</t>
+          <t>Speichern</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>pausa</t>
+          <t>Pausa</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>pause</t>
+          <t>Pause</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>fotocamera</t>
+          <t>Fotocamera</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>kamera</t>
+          <t>Kamera</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>mic</t>
+          <t>Mic</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>mic</t>
+          <t>Mic</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>titolo</t>
+          <t>Titolo</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>titel</t>
+          <t>Titel</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>notiz</t>
+          <t>Notiz</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>notizen</t>
+          <t>Notizen</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>testo</t>
+          <t>Testo</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>entrare</t>
+          <t>Entrare</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>eingeben</t>
+          <t>Eingeben</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>fatto</t>
+          <t>Fatto</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>fertig</t>
+          <t>Fertig</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>istantanea</t>
+          <t>Istantanea</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>schnappschuss</t>
+          <t>Schnappschuss</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>cattura</t>
+          <t>Cattura</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>erfassen</t>
+          <t>Erfassen</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>cattura 2D</t>
+          <t>Cattura 2D</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>cattura a 360°</t>
+          <t>Cattura a 360°</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>di più</t>
+          <t>Di più</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>mehr</t>
+          <t>Mehr</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>impostazioni</t>
+          <t>Impostazioni</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>einstellungen</t>
+          <t>Einstellungen</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2308,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>desktop</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>interrompere la condivisione dello schermo</t>
+          <t>Interrompere la condivisione dello schermo</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>bildschirmfreigabe beenden</t>
+          <t>Bildschirmfreigabe beenden</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>mostra</t>
+          <t>Mostra</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>anzeigen</t>
+          <t>Anzeigen</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>nascondere</t>
+          <t>Nascondere</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>verbergen</t>
+          <t>Verbergen</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>pOV dell'ospite</t>
+          <t>POV dell'ospite</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>gast-POV</t>
+          <t>Gast-POV</t>
         </is>
       </c>
     </row>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>Chat</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>inviare</t>
+          <t>Inviare</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>senden</t>
+          <t>Senden</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>scrivere un messaggio</t>
+          <t>Scrivere un messaggio</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>eine Nachricht schreiben</t>
+          <t>Eine Nachricht schreiben</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2506,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>caricare</t>
+          <t>Caricare</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>hochladen</t>
+          <t>Hochladen</t>
         </is>
       </c>
     </row>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>lei</t>
+          <t>Lei</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>sie</t>
+          <t>Sie</t>
         </is>
       </c>
     </row>
@@ -2572,12 +2572,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>presenta</t>
+          <t>Presenta</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>präsentiert</t>
+          <t>Präsentiert</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>è qui</t>
+          <t>È qui</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>ist hier</t>
+          <t>Ist hier</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>sono qui</t>
+          <t>Sono qui</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>sind hier</t>
+          <t>Sind hier</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Video war verzögert</t>
+          <t>Video wurde verzögert</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Apprezziamo il fatto che abbia dedicato del tempo a darci un feedback e lavoreremo per
+          <t>Apprezziamo il fatto che abbia dedicato del tempo a fornirci un feedback e lavoreremo per
           risolvere i problemi che ha elencato.</t>
         </is>
       </c>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>einreichen</t>
+          <t>Einreichen</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>registrazione</t>
+          <t>Registrazione</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>aufnahme</t>
+          <t>Aufnahme</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>spazi di lavoro</t>
+          <t>Spazi di lavoro</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>arbeitsbereiche</t>
+          <t>Arbeitsbereiche</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>cronologia</t>
+          <t>Cronologia</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>nuova riunione</t>
+          <t>Nuova riunione</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>neues Meeting</t>
+          <t>Neues Meeting</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>descrizione</t>
+          <t>Descrizione</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>beschreibung</t>
+          <t>Beschreibung</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Da</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>von</t>
+          <t>Von</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>zu</t>
+          <t>Zu</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>partecipanti</t>
+          <t>Partecipanti</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>teilnehmer</t>
+          <t>Teilnehmer</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>partecipante</t>
+          <t>Partecipante</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>teilnehmer</t>
+          <t>Teilnehmer</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>aggiungere $t(assets)</t>
+          <t>Aggiungere $t(assets)</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>scegliere dalla libreria delle risorse</t>
+          <t>Scegliere dalla libreria delle risorse</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>wählen Sie aus der Asset-Bibliothek</t>
+          <t>Wählen Sie aus der Asset-Bibliothek</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>caricare nuove risorse</t>
+          <t>Caricare nuove risorse</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>neue Assets hochladen</t>
+          <t>Neue Assets hochladen</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>modifica</t>
+          <t>Modifica</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>bearbeiten</t>
+          <t>Bearbeiten</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>selezionato</t>
+          <t>Selezionato</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>ausgewählt</t>
+          <t>Ausgewählt</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>selezionare tutti</t>
+          <t>Selezionare tutti</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>alle auswählen</t>
+          <t>Alle auswählen</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>Nome</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>dimensioni</t>
+          <t>Dimensioni</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>größe</t>
+          <t>Größe</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>typ</t>
+          <t>Typ</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>aggiornato</t>
+          <t>Aggiornato</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>aktualisiert</t>
+          <t>Aktualisiert</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>dateien</t>
+          <t>Dateien</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>datei</t>
+          <t>Datei</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>caricare i file</t>
+          <t>Caricare i file</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>dateien hochladen</t>
+          <t>Dateien hochladen</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>dettagli</t>
+          <t>Dettagli</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>details</t>
+          <t>Details</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>dettaglio $t(asset)</t>
+          <t>Dettaglio $t(asset)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>anteprima</t>
+          <t>Anteprima</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>vorschau</t>
+          <t>Vorschau</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>layout</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>layout</t>
+          <t>Layout</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>dimensione $t(file)</t>
+          <t>Dimensione $t(file)</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>domani</t>
+          <t>Domani</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>morgen</t>
+          <t>Morgen</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Passwort wurde geändert</t>
+          <t>Das Passwort wurde geändert</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>superFreeze</t>
+          <t>SuperFreeze</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>continuare</t>
+          <t>Continuare</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>weiter</t>
+          <t>Weiter</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>ha richiesto un SuperFreeze</t>
+          <t>Ha richiesto un SuperFreeze</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>hat einen SuperFreeze beantragt</t>
+          <t>Hat einen SuperFreeze beantragt</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>la richiesta di SuperFreeze è stata rifiutata</t>
+          <t>La richiesta di SuperFreeze è stata rifiutata</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>tenere</t>
+          <t>Tenere</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>halten</t>
+          <t>Halten</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>altro</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>andere</t>
+          <t>Andere</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Wenn diese Funktion aktiviert ist, können Gäste an einem Meeting teilnehmen, ohne dass ein Host anwesend ist.</t>
+          <t>Wenn diese Option aktiviert ist, können Gäste an einem Meeting teilnehmen, ohne dass ein Host anwesend ist.</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>licenze</t>
+          <t>Licenze</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>lizenzen</t>
+          <t>Lizenzen</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>stato</t>
+          <t>Stato</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>ultimo accesso</t>
+          <t>Ultimo accesso</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>letzte Anmeldung</t>
+          <t>Letzte Anmeldung</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>licenze in uso</t>
+          <t>Licenze in uso</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>verwendete Lizenzen</t>
+          <t>Verwendete Lizenzen</t>
         </is>
       </c>
     </row>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>aggiungere l'host</t>
+          <t>Aggiungere l'host</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>host hinzufügen</t>
+          <t>Host hinzufügen</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>disattivare</t>
+          <t>Disattivare</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>riattivare</t>
+          <t>Riattivare</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>disattivato</t>
+          <t>Disattivato</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>deaktiviert</t>
+          <t>Deaktiviert</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>conti host</t>
+          <t>Conti host</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>host-Konten</t>
+          <t>Host-Konten</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>dispositivi di cattura</t>
+          <t>Dispositivi di cattura</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>erfassungsgeräte</t>
+          <t>Erfassungsgeräte</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>dispositivo</t>
+          <t>Dispositivo</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>gerät</t>
+          <t>Gerät</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>dispositivi in uso</t>
+          <t>Dispositivi in uso</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>geräte im Einsatz</t>
+          <t>Geräte im Einsatz</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>numero di serie</t>
+          <t>Numero di serie</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>seriennummer</t>
+          <t>Seriennummer</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>ultimo utente</t>
+          <t>Ultimo utente</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>letzter Benutzer</t>
+          <t>Letzter Benutzer</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>ultimo utilizzo</t>
+          <t>Ultimo utilizzo</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>zuletzt verwendet</t>
+          <t>Zuletzt verwendet</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>gestire</t>
+          <t>Gestire</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>verwalten</t>
+          <t>Verwalten</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>gestire il dispositivo</t>
+          <t>Gestire il dispositivo</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>gerät verwalten</t>
+          <t>Gerät verwalten</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>host collegati</t>
+          <t>Host collegati</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>verbundene Hosts</t>
+          <t>Verbundene Hosts</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>invito</t>
+          <t>Invito</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>einladen</t>
+          <t>Einladen</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>invito inviato</t>
+          <t>Invito inviato</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>einladung verschickt</t>
+          <t>Einladung verschickt</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>attivo</t>
+          <t>Attivo</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>Aktiv</t>
         </is>
       </c>
     </row>
@@ -6670,12 +6670,12 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>inattivo</t>
+          <t>Inattivo</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>inaktiv</t>
+          <t>Inaktiv</t>
         </is>
       </c>
     </row>
@@ -6692,12 +6692,12 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>archiviato</t>
+          <t>Archiviato</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>archiviert</t>
+          <t>Archiviert</t>
         </is>
       </c>
     </row>
@@ -6714,12 +6714,12 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>prossimo</t>
+          <t>Prossimo</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>nächste</t>
+          <t>Nächste</t>
         </is>
       </c>
     </row>
@@ -6736,12 +6736,12 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>prev</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>prev</t>
+          <t>Prev</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>ricerca</t>
+          <t>Ricerca</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>suche</t>
+          <t>Suche</t>
         </is>
       </c>
     </row>
@@ -6780,12 +6780,12 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>conto</t>
+          <t>Conto</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>konto</t>
+          <t>Konto</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6824,12 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>prima</t>
+          <t>Prima</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>erste</t>
+          <t>Erste</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>trasferimento</t>
+          <t>Trasferimento</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>übertragen</t>
+          <t>Übertragen</t>
         </is>
       </c>
     </row>
@@ -6890,12 +6890,12 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>spento</t>
+          <t>Spento</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>aus</t>
+          <t>Aus</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>su</t>
+          <t>Su</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>auf</t>
+          <t>Auf</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>filtri</t>
+          <t>Filtri</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>numero totale di incontri</t>
+          <t>Numero totale di incontri</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>gesamtzahl der Meetings</t>
+          <t>Gesamtzahl der Meetings</t>
         </is>
       </c>
     </row>
@@ -7022,12 +7022,12 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>visite totali</t>
+          <t>Visite totali</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>besuche insgesamt</t>
+          <t>Besuche insgesamt</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7066,12 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>totale dei partecipanti</t>
+          <t>Totale dei partecipanti</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>teilnehmer insgesamt</t>
+          <t>Teilnehmer insgesamt</t>
         </is>
       </c>
     </row>
@@ -7088,12 +7088,12 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>feedback degli ospiti</t>
+          <t>Feedback degli ospiti</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>gäste-Feedback</t>
+          <t>Gäste-Feedback</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>durata</t>
+          <t>Durata</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>dauer</t>
+          <t>Dauer</t>
         </is>
       </c>
     </row>
@@ -7176,12 +7176,12 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Feedback</t>
         </is>
       </c>
     </row>
@@ -7220,12 +7220,12 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>datum</t>
+          <t>Datum</t>
         </is>
       </c>
     </row>
@@ -7242,12 +7242,12 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>ora di inizio</t>
+          <t>Ora di inizio</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>startzeit</t>
+          <t>Startzeit</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>analisi</t>
+          <t>Analisi</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>si è unito alla riunione</t>
+          <t>Si è unito alla riunione</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>an dem Meeting teilgenommen</t>
+          <t>An dem Meeting teilgenommen</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>ha lasciato la riunione</t>
+          <t>Ha lasciato la riunione</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>verließ das Meeting</t>
+          <t>Verließ das Meeting</t>
         </is>
       </c>
     </row>
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>ha presentato una fotocamera secondaria</t>
+          <t>Ha presentato una fotocamera secondaria</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>eine zweite Kamera präsentiert</t>
+          <t>Eine zweite Kamera präsentiert</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>ha interrotto la condivisione della fotocamera</t>
+          <t>Ha interrotto la condivisione della fotocamera</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>kamerafreigabe gestoppt</t>
+          <t>Kamerafreigabe gestoppt</t>
         </is>
       </c>
     </row>
@@ -7462,12 +7462,12 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>ha iniziato a condividere un bene</t>
+          <t>Ha iniziato a condividere un bene</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>begonnen, ein Asset zu teilen</t>
+          <t>Begonnen, ein Asset zu teilen</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>ha smesso di condividere un bene</t>
+          <t>Ha smesso di condividere un bene</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>die gemeinsame Nutzung eines Assets eingestellt hat</t>
+          <t>Die gemeinsame Nutzung eines Assets eingestellt hat</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>riprende un asset</t>
+          <t>Riprende un asset</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>ha messo in pausa una risorsa</t>
+          <t>Ha messo in pausa una risorsa</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>ha finito di presentare</t>
+          <t>Ha finito di presentare</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>fertig präsentiert</t>
+          <t>Fertig präsentiert</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>ha iniziato a presentare</t>
+          <t>Ha iniziato a presentare</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>begann zu präsentieren</t>
+          <t>Begann zu präsentieren</t>
         </is>
       </c>
     </row>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>ha messo in pausa il video</t>
+          <t>Ha messo in pausa il video</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>hat das Video angehalten</t>
+          <t>Hat das Video angehalten</t>
         </is>
       </c>
     </row>
@@ -7616,12 +7616,12 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>riprende il video</t>
+          <t>Riprende il video</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>hat das Video wieder aufgenommen</t>
+          <t>Hat das Video wieder aufgenommen</t>
         </is>
       </c>
     </row>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>hanno iniziato a condividere il loro schermo</t>
+          <t>Hanno iniziato a condividere il loro schermo</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>begonnen, ihren Bildschirm zu teilen</t>
+          <t>Begonnen, ihren Bildschirm zu teilen</t>
         </is>
       </c>
     </row>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>ha smesso di condividere il proprio schermo</t>
+          <t>Ha smesso di condividere il proprio schermo</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>ihren Bildschirm nicht mehr teilen</t>
+          <t>Ihren Bildschirm nicht mehr teilen</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>telecamera scollegata</t>
+          <t>Telecamera scollegata</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>kamera ausgeschaltet</t>
+          <t>Kamera ausgeschaltet</t>
         </is>
       </c>
     </row>
@@ -7704,12 +7704,12 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>avviso di batteria scarica della fotocamera</t>
+          <t>Avviso di batteria scarica della fotocamera</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>warnung bei niedrigem Batteriestand der Kamera</t>
+          <t>Warnung bei niedrigem Batteriestand der Kamera</t>
         </is>
       </c>
     </row>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>feed della telecamera in pausa</t>
+          <t>Feed della telecamera in pausa</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>angehaltene Kameraführung</t>
+          <t>Angehaltene Kameraführung</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>ripresa della telecamera</t>
+          <t>Ripresa della telecamera</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>kameraführung wieder aufgenommen</t>
+          <t>Kameraführung wieder aufgenommen</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>focus sugli ospiti bloccati</t>
+          <t>Focus sugli ospiti bloccati</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>gesperrter Fokus der Gäste</t>
+          <t>Gesperrter Fokus der Gäste</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>l'attenzione degli ospiti è stata sbloccata</t>
+          <t>L'attenzione degli ospiti è stata sbloccata</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>freigegebener Fokus der Gäste</t>
+          <t>Freigegebener Fokus der Gäste</t>
         </is>
       </c>
     </row>
@@ -7836,12 +7836,12 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>presentato utilizzando lo strumento spotlight</t>
+          <t>Presentato utilizzando lo strumento spotlight</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>präsentiert mit dem Spotlight-Tool</t>
+          <t>Präsentiert mit dem Spotlight-Tool</t>
         </is>
       </c>
     </row>
@@ -7858,12 +7858,12 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>ha smesso di presentare Spotlight</t>
+          <t>Ha smesso di presentare Spotlight</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>hat aufgehört, Spotlight zu präsentieren</t>
+          <t>Hat aufgehört, Spotlight zu präsentieren</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>nuova password</t>
+          <t>Nuova password</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>neues Passwort</t>
+          <t>Neues Passwort</t>
         </is>
       </c>
     </row>
@@ -7902,12 +7902,12 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>confermi la nuova password</t>
+          <t>Confermi la nuova password</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>neues Passwort bestätigen</t>
+          <t>Neues Passwort bestätigen</t>
         </is>
       </c>
     </row>
@@ -7924,12 +7924,12 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>indirizzo e-mail</t>
+          <t>Indirizzo e-mail</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>e-Mail Adresse</t>
+          <t>E-Mail Adresse</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>password temporanea</t>
+          <t>Password temporanea</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>temporäres Passwort</t>
+          <t>Temporäres Passwort</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>reimpostare la password</t>
+          <t>Reimpostare la password</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>passwort zurücksetzen</t>
+          <t>Passwort zurücksetzen</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>Wenn ein Konto mit dieser E-Mail-Adresse existiert, wurde ein Link zum Zurücksetzen des Passworts gesendet. Bitte &lt;1&gt; check
+          <t>Wenn ein Konto mit dieser E-Mail existiert, wurde ein Link zum Zurücksetzen des Passworts gesendet. Bitte &lt;1&gt; check
  your spam folder &lt;/1&gt;, wenn Sie ihn nicht in Ihrem Posteingang erhalten.</t>
         </is>
       </c>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o contatti &lt;0&gt;support@avatour.live&lt;/0&gt; per ricevere assistenza.</t>
+          <t>Oops! Qualcosa è andato storto durante il tentativo di reimpostare la sua password. Riprovi più tardi o si rivolga a &lt;0&gt;support@avatour.live&lt;/0&gt; per ricevere assistenza.</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>password dimenticata</t>
+          <t>Password dimenticata</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>passwort vergessen</t>
+          <t>Passwort vergessen</t>
         </is>
       </c>
     </row>
@@ -8344,12 +8344,12 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>abmelden</t>
+          <t>Abmelden</t>
         </is>
       </c>
     </row>
@@ -8388,12 +8388,12 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>minuti totali</t>
+          <t>Minuti totali</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>gesamtminuten</t>
+          <t>Gesamtminuten</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8410,12 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>ore di visita totali</t>
+          <t>Ore di visita totali</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>besuchsstunden insgesamt</t>
+          <t>Besuchsstunden insgesamt</t>
         </is>
       </c>
     </row>
@@ -8432,12 +8432,12 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>codice spettatore</t>
+          <t>Codice spettatore</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>zuschauercode</t>
+          <t>Zuschauercode</t>
         </is>
       </c>
     </row>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>copia il link dello spettatore</t>
+          <t>Copia il link dello spettatore</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>zuschauerlink kopieren</t>
+          <t>Zuschauerlink kopieren</t>
         </is>
       </c>
     </row>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>dominio</t>
+          <t>Dominio</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>domain</t>
+          <t>Domain</t>
         </is>
       </c>
     </row>
@@ -8718,12 +8718,12 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>rimuovere</t>
+          <t>Rimuovere</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>entfernen</t>
+          <t>Entfernen</t>
         </is>
       </c>
     </row>
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>colore attuale</t>
+          <t>Colore attuale</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>aktuelle Farbe</t>
+          <t>Aktuelle Farbe</t>
         </is>
       </c>
     </row>
@@ -8762,12 +8762,12 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>logo</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>logo</t>
+          <t>Logo</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>logo attuale</t>
+          <t>Logo attuale</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>aktuelles Logo</t>
+          <t>Aktuelles Logo</t>
         </is>
       </c>
     </row>
@@ -8828,12 +8828,12 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>icona quadrata</t>
+          <t>Icona quadrata</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>quadratisches Symbol</t>
+          <t>Quadratisches Symbol</t>
         </is>
       </c>
     </row>
@@ -8872,12 +8872,12 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>icona corrente</t>
+          <t>Icona corrente</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>aktuelles Symbol</t>
+          <t>Aktuelles Symbol</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>immagine di sfondo</t>
+          <t>Immagine di sfondo</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>hintergrundbild</t>
+          <t>Hintergrundbild</t>
         </is>
       </c>
     </row>
@@ -8938,12 +8938,12 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>immagine attuale</t>
+          <t>Immagine attuale</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>aktuelles Bild</t>
+          <t>Aktuelles Bild</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>immagine di sfondo 360 (per le cuffie VR)</t>
+          <t>Immagine di sfondo 360 (per le cuffie VR)</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Formato JPG o PNG. Deve essere un'immagine equidistante a 360° con una larghezza minima di 3000px.</t>
+          <t>Formato JPG o PNG. Deve essere un'immagine equirettangolare a 360° con una larghezza minima di 3000px.</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>colore di sovrapposizione</t>
+          <t>Colore di sovrapposizione</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>overlay-Farbe</t>
+          <t>Overlay-Farbe</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>info sulla riunione</t>
+          <t>Info sulla riunione</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>meeting-Informationen</t>
+          <t>Meeting-Informationen</t>
         </is>
       </c>
     </row>
@@ -9532,12 +9532,12 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>partecipare alla riunione</t>
+          <t>Partecipare alla riunione</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>meeting beitreten</t>
+          <t>Meeting beitreten</t>
         </is>
       </c>
     </row>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>titolo dell'area di lavoro</t>
+          <t>Titolo dell'area di lavoro</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>arbeitsbereich Titel</t>
+          <t>Arbeitsbereich Titel</t>
         </is>
       </c>
     </row>
@@ -9818,12 +9818,12 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>salvare l'area di lavoro</t>
+          <t>Salvare l'area di lavoro</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>arbeitsbereich speichern</t>
+          <t>Arbeitsbereich speichern</t>
         </is>
       </c>
     </row>
@@ -9840,12 +9840,12 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>eliminare lo spazio di lavoro</t>
+          <t>Eliminare lo spazio di lavoro</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>arbeitsbereich löschen</t>
+          <t>Arbeitsbereich löschen</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9862,12 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>programma</t>
+          <t>Programma</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>zeitplan</t>
+          <t>Zeitplan</t>
         </is>
       </c>
     </row>
@@ -9884,12 +9884,12 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>visualizza i dettagli</t>
+          <t>Visualizza i dettagli</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>details anzeigen</t>
+          <t>Details anzeigen</t>
         </is>
       </c>
     </row>
@@ -9928,12 +9928,12 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>è stato invitato con successo</t>
+          <t>È stato invitato con successo</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>wurde erfolgreich eingeladen</t>
+          <t>Wurde erfolgreich eingeladen</t>
         </is>
       </c>
     </row>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>entrare nell'area di lavoro</t>
+          <t>Entrare nell'area di lavoro</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>arbeitsbereich betreten</t>
+          <t>Arbeitsbereich betreten</t>
         </is>
       </c>
     </row>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>unirsi alla sala riunioni</t>
+          <t>Unirsi alla sala riunioni</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>meeting-Raum beitreten</t>
+          <t>Meeting-Raum beitreten</t>
         </is>
       </c>
     </row>
@@ -10038,12 +10038,12 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>riunione di uscita</t>
+          <t>Riunione di uscita</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>exit Meeting</t>
+          <t>Exit Meeting</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>spazio di lavoro dell'archivio</t>
+          <t>Spazio di lavoro dell'archivio</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>archiv-Arbeitsbereich</t>
+          <t>Archiv-Arbeitsbereich</t>
         </is>
       </c>
     </row>
@@ -10082,12 +10082,12 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>disarchiviare lo spazio di lavoro</t>
+          <t>Disarchiviare lo spazio di lavoro</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>arbeitsbereich entarchivieren</t>
+          <t>Arbeitsbereich entarchivieren</t>
         </is>
       </c>
     </row>
@@ -10104,12 +10104,12 @@
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>prossima riunione</t>
+          <t>Prossima riunione</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>nächstes Meeting</t>
+          <t>Nächstes Meeting</t>
         </is>
       </c>
     </row>
@@ -10148,12 +10148,12 @@
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>link scaduto</t>
+          <t>Link scaduto</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>link verfallen</t>
+          <t>Link verfallen</t>
         </is>
       </c>
     </row>
@@ -10302,12 +10302,12 @@
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>tutti i tipi</t>
+          <t>Tutti i tipi</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>alle Typen</t>
+          <t>Alle Typen</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>ordina per</t>
+          <t>Ordina per</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>sortieren nach</t>
+          <t>Sortieren nach</t>
         </is>
       </c>
     </row>
@@ -10346,12 +10346,12 @@
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>vedi tutti</t>
+          <t>Vedi tutti</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>alle anzeigen</t>
+          <t>Alle anzeigen</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>iniziare la riunione</t>
+          <t>Iniziare la riunione</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>meeting beginnen</t>
+          <t>Meeting beginnen</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>impostazioni della riunione</t>
+          <t>Impostazioni della riunione</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>meeting-Einstellungen</t>
+          <t>Meeting-Einstellungen</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>Die Reisedistanz wird als Großkreisdistanz zwischen dem Standort des Erfassungsgeräts und dem Standort jedes Fernteilnehmers geschätzt und mit 2 multipliziert, um die Hin- und Rückreise zu berücksichtigen. Die Standortdaten werden über GPS, den Browserstandort oder die IP-Adresse ermittelt.</t>
+          <t>Die Reisedistanz wird als Großkreisdistanz zwischen dem Standort des Erfassungsgeräts und dem Standort jedes Fernteilnehmers geschätzt und mit 2 multipliziert, um die Hin- und Rückreise zu berücksichtigen. Die Standortdaten werden von GPS, dem Browserstandort oder der IP-Adresse abgeleitet.</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>equivalente a &lt;0&gt;{{trees}} trees&lt;/0&gt;</t>
+          <t>Equivalente a &lt;0&gt;{{trees}} trees&lt;/0&gt;</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>posizione</t>
+          <t>Posizione</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>standort</t>
+          <t>Standort</t>
         </is>
       </c>
     </row>
@@ -10889,12 +10889,12 @@
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>modifica i dettagli</t>
+          <t>Modifica i dettagli</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>details bearbeiten</t>
+          <t>Details bearbeiten</t>
         </is>
       </c>
     </row>
@@ -10999,12 +10999,12 @@
       </c>
       <c r="C478" s="3" t="inlineStr">
         <is>
-          <t>e-mail di lavoro</t>
+          <t>E-mail di lavoro</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>arbeits-E-Mail</t>
+          <t>Arbeits-E-Mail</t>
         </is>
       </c>
     </row>
@@ -11021,12 +11021,12 @@
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>licenza</t>
+          <t>Licenza</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>lizenz</t>
+          <t>Lizenz</t>
         </is>
       </c>
     </row>
@@ -11263,12 +11263,12 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>ha messo in pausa il video per prendere nota.</t>
+          <t>Ha messo in pausa il video per prendere nota.</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>hat das Video angehalten, um eine Notiz zu machen.</t>
+          <t>Hat das Video angehalten, um eine Notiz zu machen.</t>
         </is>
       </c>
     </row>
@@ -11285,12 +11285,12 @@
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>salvare il nome</t>
+          <t>Salvare il nome</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>name speichern</t>
+          <t>Name speichern</t>
         </is>
       </c>
     </row>
@@ -11307,12 +11307,12 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>cambiare nome</t>
+          <t>Cambiare nome</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>name ändern</t>
+          <t>Name ändern</t>
         </is>
       </c>
     </row>
